--- a/artfynd/A 38629-2026 artfynd.xlsx
+++ b/artfynd/A 38629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481171</v>
       </c>
       <c r="B2" t="n">
-        <v>104869</v>
+        <v>104874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136481239</v>
       </c>
       <c r="B3" t="n">
-        <v>98219</v>
+        <v>98224</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38629-2026 artfynd.xlsx
+++ b/artfynd/A 38629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481171</v>
       </c>
       <c r="B2" t="n">
-        <v>104874</v>
+        <v>104876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136481239</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>98226</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38629-2026 artfynd.xlsx
+++ b/artfynd/A 38629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481171</v>
       </c>
       <c r="B2" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136481239</v>
       </c>
       <c r="B3" t="n">
-        <v>98226</v>
+        <v>98232</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38629-2026 artfynd.xlsx
+++ b/artfynd/A 38629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481171</v>
       </c>
       <c r="B2" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136481239</v>
       </c>
       <c r="B3" t="n">
-        <v>98232</v>
+        <v>98234</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38629-2026 artfynd.xlsx
+++ b/artfynd/A 38629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481171</v>
       </c>
       <c r="B2" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136481239</v>
       </c>
       <c r="B3" t="n">
-        <v>98234</v>
+        <v>98235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38629-2026 artfynd.xlsx
+++ b/artfynd/A 38629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481171</v>
       </c>
       <c r="B2" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136481239</v>
       </c>
       <c r="B3" t="n">
-        <v>98235</v>
+        <v>98241</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38629-2026 artfynd.xlsx
+++ b/artfynd/A 38629-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481171</v>
       </c>
       <c r="B2" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136481239</v>
       </c>
       <c r="B3" t="n">
-        <v>98241</v>
+        <v>98245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
